--- a/GCC_CRM.xlsx
+++ b/GCC_CRM.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Özet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRM'!$A$1:$M$426</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRM'!$A$1:$M$451</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M426"/>
+  <dimension ref="A1:M451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -23035,8 +23035,1233 @@
       <c r="L426" s="3" t="inlineStr"/>
       <c r="M426" s="3" t="inlineStr"/>
     </row>
+    <row r="427" ht="26" customHeight="1">
+      <c r="A427" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C427" s="3" t="inlineStr">
+        <is>
+          <t>Shakour AbuGhazalah</t>
+        </is>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="inlineStr">
+        <is>
+          <t>Albaik</t>
+        </is>
+      </c>
+      <c r="F427" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G427" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H427" s="3" t="inlineStr"/>
+      <c r="I427" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Shakour%20AbuGhazalah%20Albaik</t>
+        </is>
+      </c>
+      <c r="J427" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K427" s="3" t="inlineStr"/>
+      <c r="L427" s="3" t="inlineStr"/>
+      <c r="M427" s="3" t="inlineStr"/>
+    </row>
+    <row r="428" ht="26" customHeight="1">
+      <c r="A428" s="2" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>Talal Maddah</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="inlineStr">
+        <is>
+          <t>Funoon al Jazeera</t>
+        </is>
+      </c>
+      <c r="F428" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G428" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H428" s="3" t="inlineStr"/>
+      <c r="I428" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Talal%20Maddah%20Funoon%20al%20Jazeera</t>
+        </is>
+      </c>
+      <c r="J428" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K428" s="3" t="inlineStr"/>
+      <c r="L428" s="3" t="inlineStr"/>
+      <c r="M428" s="3" t="inlineStr"/>
+    </row>
+    <row r="429" ht="26" customHeight="1">
+      <c r="A429" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="inlineStr">
+        <is>
+          <t>Saud of Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E429" s="3" t="inlineStr">
+        <is>
+          <t>General Intelligence Presidency</t>
+        </is>
+      </c>
+      <c r="F429" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G429" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H429" s="3" t="inlineStr"/>
+      <c r="I429" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Saud%20of%20Saudi%20Arabia%20General%20Intelligence%20Presidency</t>
+        </is>
+      </c>
+      <c r="J429" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K429" s="3" t="inlineStr"/>
+      <c r="L429" s="3" t="inlineStr"/>
+      <c r="M429" s="3" t="inlineStr"/>
+    </row>
+    <row r="430" ht="26" customHeight="1">
+      <c r="A430" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="inlineStr">
+        <is>
+          <t>Saud al-Kabeer</t>
+        </is>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E430" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabian Royal Guard</t>
+        </is>
+      </c>
+      <c r="F430" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G430" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H430" s="3" t="inlineStr"/>
+      <c r="I430" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Saud%20al-Kabeer%20Saudi%20Arabian%20Royal%20Guard</t>
+        </is>
+      </c>
+      <c r="J430" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K430" s="3" t="inlineStr"/>
+      <c r="L430" s="3" t="inlineStr"/>
+      <c r="M430" s="3" t="inlineStr"/>
+    </row>
+    <row r="431" ht="26" customHeight="1">
+      <c r="A431" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="inlineStr">
+        <is>
+          <t>Mohammed Ali Zainal</t>
+        </is>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E431" s="3" t="inlineStr">
+        <is>
+          <t>Al-Falah School</t>
+        </is>
+      </c>
+      <c r="F431" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G431" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H431" s="3" t="inlineStr"/>
+      <c r="I431" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Mohammed%20Ali%20Zainal%20Al-Falah%20School</t>
+        </is>
+      </c>
+      <c r="J431" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K431" s="3" t="inlineStr"/>
+      <c r="L431" s="3" t="inlineStr"/>
+      <c r="M431" s="3" t="inlineStr"/>
+    </row>
+    <row r="432" ht="26" customHeight="1">
+      <c r="A432" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>Mohammed Saleh al-Bejadi</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E432" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Civil and Political Rights Association</t>
+        </is>
+      </c>
+      <c r="F432" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G432" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H432" s="3" t="inlineStr"/>
+      <c r="I432" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Mohammed%20Saleh%20al-Bejadi%20Saudi%20Civil%20and%20Political%20Rights%20Association</t>
+        </is>
+      </c>
+      <c r="J432" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K432" s="3" t="inlineStr"/>
+      <c r="L432" s="3" t="inlineStr"/>
+      <c r="M432" s="3" t="inlineStr"/>
+    </row>
+    <row r="433" ht="26" customHeight="1">
+      <c r="A433" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="inlineStr">
+        <is>
+          <t>Abdulrahman al-Hamid</t>
+        </is>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E433" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Civil and Political Rights Association</t>
+        </is>
+      </c>
+      <c r="F433" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G433" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H433" s="3" t="inlineStr"/>
+      <c r="I433" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Abdulrahman%20al-Hamid%20Saudi%20Civil%20and%20Political%20Rights%20Association</t>
+        </is>
+      </c>
+      <c r="J433" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K433" s="3" t="inlineStr"/>
+      <c r="L433" s="3" t="inlineStr"/>
+      <c r="M433" s="3" t="inlineStr"/>
+    </row>
+    <row r="434" ht="26" customHeight="1">
+      <c r="A434" s="2" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>Khalid bin Mahfouz</t>
+        </is>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="inlineStr">
+        <is>
+          <t>Muwaqaf</t>
+        </is>
+      </c>
+      <c r="F434" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G434" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H434" s="3" t="inlineStr"/>
+      <c r="I434" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Khalid%20bin%20Mahfouz%20Muwaqaf</t>
+        </is>
+      </c>
+      <c r="J434" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K434" s="3" t="inlineStr"/>
+      <c r="L434" s="3" t="inlineStr"/>
+      <c r="M434" s="3" t="inlineStr"/>
+    </row>
+    <row r="435" ht="26" customHeight="1">
+      <c r="A435" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>Zeid Al-Ja'ba</t>
+        </is>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="inlineStr">
+        <is>
+          <t>Al-Nassr</t>
+        </is>
+      </c>
+      <c r="F435" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G435" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H435" s="3" t="inlineStr"/>
+      <c r="I435" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Zeid%20Al-Ja%27ba%20Al-Nassr</t>
+        </is>
+      </c>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K435" s="3" t="inlineStr"/>
+      <c r="L435" s="3" t="inlineStr"/>
+      <c r="M435" s="3" t="inlineStr"/>
+    </row>
+    <row r="436" ht="26" customHeight="1">
+      <c r="A436" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>Saud bin Faisal bin Abdulaziz Al Saud</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>Prince Saud Al-Faisal Institute for Diplomatic Studies</t>
+        </is>
+      </c>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G436" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H436" s="3" t="inlineStr"/>
+      <c r="I436" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Saud%20bin%20Faisal%20bin%20Abdulaziz%20Al%20Saud%20Prince%20Saud%20Al-Faisal%20Institute%20for%20Diplomatic%20Studies</t>
+        </is>
+      </c>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K436" s="3" t="inlineStr"/>
+      <c r="L436" s="3" t="inlineStr"/>
+      <c r="M436" s="3" t="inlineStr"/>
+    </row>
+    <row r="437" ht="26" customHeight="1">
+      <c r="A437" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>Shahrān ibn ʻifris</t>
+        </is>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="inlineStr">
+        <is>
+          <t>Shahran</t>
+        </is>
+      </c>
+      <c r="F437" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G437" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H437" s="3" t="inlineStr"/>
+      <c r="I437" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Shahr%C4%81n%20ibn%20%CA%BBifris%20Shahran</t>
+        </is>
+      </c>
+      <c r="J437" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K437" s="3" t="inlineStr"/>
+      <c r="L437" s="3" t="inlineStr"/>
+      <c r="M437" s="3" t="inlineStr"/>
+    </row>
+    <row r="438" ht="26" customHeight="1">
+      <c r="A438" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>Sultan bin Abdulaziz</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>Sultan bin Abdulaziz Al Saud Foundation</t>
+        </is>
+      </c>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G438" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H438" s="3" t="inlineStr"/>
+      <c r="I438" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sultan%20bin%20Abdulaziz%20Sultan%20bin%20Abdulaziz%20Al%20Saud%20Foundation</t>
+        </is>
+      </c>
+      <c r="J438" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K438" s="3" t="inlineStr"/>
+      <c r="L438" s="3" t="inlineStr"/>
+      <c r="M438" s="3" t="inlineStr"/>
+    </row>
+    <row r="439" ht="26" customHeight="1">
+      <c r="A439" s="2" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C439" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Fahad al-Qahtani</t>
+        </is>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Civil and Political Rights Association</t>
+        </is>
+      </c>
+      <c r="F439" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G439" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H439" s="3" t="inlineStr"/>
+      <c r="I439" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Mohammad%20Fahad%20al-Qahtani%20Saudi%20Civil%20and%20Political%20Rights%20Association</t>
+        </is>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K439" s="3" t="inlineStr"/>
+      <c r="L439" s="3" t="inlineStr"/>
+      <c r="M439" s="3" t="inlineStr"/>
+    </row>
+    <row r="440" ht="26" customHeight="1">
+      <c r="A440" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>Władysław Szpilman</t>
+        </is>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="inlineStr">
+        <is>
+          <t>Intervision Song Contest</t>
+        </is>
+      </c>
+      <c r="F440" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G440" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H440" s="3" t="inlineStr"/>
+      <c r="I440" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=W%C5%82adys%C5%82aw%20Szpilman%20Intervision%20Song%20Contest</t>
+        </is>
+      </c>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K440" s="3" t="inlineStr"/>
+      <c r="L440" s="3" t="inlineStr"/>
+      <c r="M440" s="3" t="inlineStr"/>
+    </row>
+    <row r="441" ht="26" customHeight="1">
+      <c r="A441" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>Masayoshi Son</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>SoftBank Vision Fund</t>
+        </is>
+      </c>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G441" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H441" s="3" t="inlineStr"/>
+      <c r="I441" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Masayoshi%20Son%20SoftBank%20Vision%20Fund</t>
+        </is>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K441" s="3" t="inlineStr"/>
+      <c r="L441" s="3" t="inlineStr"/>
+      <c r="M441" s="3" t="inlineStr"/>
+    </row>
+    <row r="442" ht="26" customHeight="1">
+      <c r="A442" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="inlineStr">
+        <is>
+          <t>Hugo Cugnet</t>
+        </is>
+      </c>
+      <c r="D442" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E442" s="3" t="inlineStr">
+        <is>
+          <t>Wusool Capital</t>
+        </is>
+      </c>
+      <c r="F442" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G442" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H442" s="3" t="inlineStr"/>
+      <c r="I442" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Hugo%20Cugnet%20Wusool%20Capital</t>
+        </is>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K442" s="3" t="inlineStr"/>
+      <c r="L442" s="3" t="inlineStr"/>
+      <c r="M442" s="3" t="inlineStr"/>
+    </row>
+    <row r="443" ht="26" customHeight="1">
+      <c r="A443" s="2" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>Sarah Koben</t>
+        </is>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="inlineStr">
+        <is>
+          <t>Saint Objets</t>
+        </is>
+      </c>
+      <c r="F443" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G443" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H443" s="3" t="inlineStr"/>
+      <c r="I443" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sarah%20Koben%20Saint%20Objets</t>
+        </is>
+      </c>
+      <c r="J443" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K443" s="3" t="inlineStr"/>
+      <c r="L443" s="3" t="inlineStr"/>
+      <c r="M443" s="3" t="inlineStr"/>
+    </row>
+    <row r="444" ht="26" customHeight="1">
+      <c r="A444" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian Scheplitz</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>Deckmetric</t>
+        </is>
+      </c>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G444" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H444" s="3" t="inlineStr"/>
+      <c r="I444" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sebastian%20Scheplitz%20Deckmetric</t>
+        </is>
+      </c>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K444" s="3" t="inlineStr"/>
+      <c r="L444" s="3" t="inlineStr"/>
+      <c r="M444" s="3" t="inlineStr"/>
+    </row>
+    <row r="445" ht="26" customHeight="1">
+      <c r="A445" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="inlineStr">
+        <is>
+          <t>Tim Jacobs</t>
+        </is>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="inlineStr">
+        <is>
+          <t>KTS Global</t>
+        </is>
+      </c>
+      <c r="F445" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G445" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H445" s="3" t="inlineStr"/>
+      <c r="I445" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Tim%20Jacobs%20KTS%20Global</t>
+        </is>
+      </c>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K445" s="3" t="inlineStr"/>
+      <c r="L445" s="3" t="inlineStr"/>
+      <c r="M445" s="3" t="inlineStr"/>
+    </row>
+    <row r="446" ht="26" customHeight="1">
+      <c r="A446" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>Camilla Wirth</t>
+        </is>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>friction AI</t>
+        </is>
+      </c>
+      <c r="F446" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G446" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H446" s="3" t="inlineStr"/>
+      <c r="I446" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Camilla%20Wirth%20friction%20AI</t>
+        </is>
+      </c>
+      <c r="J446" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K446" s="3" t="inlineStr"/>
+      <c r="L446" s="3" t="inlineStr"/>
+      <c r="M446" s="3" t="inlineStr"/>
+    </row>
+    <row r="447" ht="26" customHeight="1">
+      <c r="A447" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="inlineStr">
+        <is>
+          <t>Hanane Benkhallouk</t>
+        </is>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="inlineStr">
+        <is>
+          <t>Sustain Leadership Consultancy</t>
+        </is>
+      </c>
+      <c r="F447" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G447" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H447" s="3" t="inlineStr"/>
+      <c r="I447" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Hanane%20Benkhallouk%20Sustain%20Leadership%20Consultancy</t>
+        </is>
+      </c>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K447" s="3" t="inlineStr"/>
+      <c r="L447" s="3" t="inlineStr"/>
+      <c r="M447" s="3" t="inlineStr"/>
+    </row>
+    <row r="448" ht="26" customHeight="1">
+      <c r="A448" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="inlineStr">
+        <is>
+          <t>Hanane Benkhallouk</t>
+        </is>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="inlineStr">
+        <is>
+          <t>Tawazoun</t>
+        </is>
+      </c>
+      <c r="F448" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G448" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H448" s="3" t="inlineStr"/>
+      <c r="I448" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Hanane%20Benkhallouk%20Tawazoun</t>
+        </is>
+      </c>
+      <c r="J448" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K448" s="3" t="inlineStr"/>
+      <c r="L448" s="3" t="inlineStr"/>
+      <c r="M448" s="3" t="inlineStr"/>
+    </row>
+    <row r="449" ht="26" customHeight="1">
+      <c r="A449" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>Neill Frank</t>
+        </is>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="inlineStr">
+        <is>
+          <t>Pythia Technologies</t>
+        </is>
+      </c>
+      <c r="F449" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G449" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H449" s="3" t="inlineStr"/>
+      <c r="I449" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Neill%20Frank%20Pythia%20Technologies</t>
+        </is>
+      </c>
+      <c r="J449" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K449" s="3" t="inlineStr"/>
+      <c r="L449" s="3" t="inlineStr"/>
+      <c r="M449" s="3" t="inlineStr"/>
+    </row>
+    <row r="450" ht="26" customHeight="1">
+      <c r="A450" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>Sophie Solmini</t>
+        </is>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="inlineStr">
+        <is>
+          <t>Elite Resilience Coaching</t>
+        </is>
+      </c>
+      <c r="F450" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G450" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H450" s="3" t="inlineStr"/>
+      <c r="I450" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sophie%20Solmini%20Elite%20Resilience%20Coaching</t>
+        </is>
+      </c>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K450" s="3" t="inlineStr"/>
+      <c r="L450" s="3" t="inlineStr"/>
+      <c r="M450" s="3" t="inlineStr"/>
+    </row>
+    <row r="451" ht="26" customHeight="1">
+      <c r="A451" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>Wikidata kesif (bot)</t>
+        </is>
+      </c>
+      <c r="C451" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Mahmood</t>
+        </is>
+      </c>
+      <c r="D451" s="3" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="E451" s="3" t="inlineStr">
+        <is>
+          <t>Plug Media</t>
+        </is>
+      </c>
+      <c r="F451" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G451" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="H451" s="3" t="inlineStr"/>
+      <c r="I451" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Ahmad%20Mahmood%20Plug%20Media</t>
+        </is>
+      </c>
+      <c r="J451" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K451" s="3" t="inlineStr"/>
+      <c r="L451" s="3" t="inlineStr"/>
+      <c r="M451" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M426"/>
+  <autoFilter ref="A1:M451"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23069,7 +24294,7 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5">
@@ -23100,7 +24325,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>2026-06-10 14:12</t>
+          <t>2026-06-10 12:45</t>
         </is>
       </c>
     </row>
